--- a/CaesarCipher/Документация/Материалы/Схема.xlsx
+++ b/CaesarCipher/Документация/Материалы/Схема.xlsx
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>+CheckText(text) : bool</t>
-  </si>
-  <si>
-    <t>+OutputResult(originalText, encryptedText) : void</t>
   </si>
   <si>
     <t>&lt;&lt;WinForm&gt;&gt;/MainFom</t>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>-alphabet_ : Alphabet</t>
+  </si>
+  <si>
+    <t>+OutputResult(originalText, encryptedText, filePath, key) : void</t>
   </si>
 </sst>
 </file>
@@ -373,44 +373,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>221457</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>341045</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>200284</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Рисунок 3"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20378738" y="3767138"/>
-          <a:ext cx="3762901" cy="1862396"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>292894</xdr:colOff>
       <xdr:row>7</xdr:row>
@@ -430,7 +392,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -468,7 +430,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -644,28 +606,28 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>341046</xdr:colOff>
+      <xdr:colOff>588686</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>221587</xdr:rowOff>
+      <xdr:rowOff>212036</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
       <xdr:colOff>292895</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>221856</xdr:rowOff>
+      <xdr:rowOff>217092</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
         <xdr:cNvPr id="28" name="Соединительная линия уступом 27"/>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="5" idx="1"/>
-          <a:endCxn id="4" idx="3"/>
+          <a:endCxn id="10" idx="3"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="10800000">
-          <a:off x="24141640" y="4698337"/>
-          <a:ext cx="1773505" cy="269"/>
+          <a:off x="25246530" y="4688786"/>
+          <a:ext cx="1525865" cy="5056"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
@@ -1234,20 +1196,58 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>202406</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>535782</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>202406</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>535055</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>77002</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>588685</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>7353</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="61" name="Рисунок 60"/>
+        <xdr:cNvPr id="10" name="Рисунок 9"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21550313" y="3940969"/>
+          <a:ext cx="3696216" cy="1495634"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>206342</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>798</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Рисунок 13"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1260,8 +1260,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25217437" y="8834438"/>
-          <a:ext cx="11869806" cy="5744377"/>
+          <a:off x="27693938" y="11168063"/>
+          <a:ext cx="11136279" cy="5715798"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1541,7 +1541,7 @@
   <cols>
     <col min="2" max="2" width="21" customWidth="1"/>
     <col min="4" max="4" width="46.28515625" customWidth="1"/>
-    <col min="6" max="6" width="55.42578125" customWidth="1"/>
+    <col min="6" max="6" width="68.140625" customWidth="1"/>
     <col min="8" max="8" width="56.42578125" customWidth="1"/>
     <col min="10" max="10" width="59.42578125" customWidth="1"/>
   </cols>
@@ -1602,11 +1602,11 @@
       </c>
       <c r="G2" s="7"/>
       <c r="H2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I2" s="7"/>
       <c r="J2" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K2" s="7"/>
       <c r="L2" s="7"/>
@@ -1651,11 +1651,11 @@
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
       <c r="H3" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="7"/>
@@ -1702,11 +1702,11 @@
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="I4" s="7"/>
       <c r="J4" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -1751,11 +1751,11 @@
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="7"/>
@@ -1800,11 +1800,11 @@
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -1849,11 +1849,11 @@
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -1892,15 +1892,15 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="3" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I8" s="7"/>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1941,11 +1941,11 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1986,7 +1986,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I10" s="7"/>
       <c r="J10" s="7"/>
@@ -2029,7 +2029,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
@@ -2072,7 +2072,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
@@ -2115,7 +2115,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="I13" s="7"/>
       <c r="J13" s="7"/>
@@ -2158,7 +2158,7 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" s="7"/>
       <c r="J14" s="7"/>
@@ -2201,7 +2201,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
@@ -2244,7 +2244,7 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I16" s="7"/>
       <c r="J16" s="7"/>
@@ -2287,7 +2287,7 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I17" s="7"/>
       <c r="J17" s="7"/>
@@ -2330,7 +2330,7 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I18" s="7"/>
       <c r="J18" s="7"/>
@@ -2373,7 +2373,7 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="7"/>
       <c r="J19" s="7"/>
@@ -2416,7 +2416,7 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I20" s="7"/>
       <c r="J20" s="7"/>
@@ -2459,7 +2459,7 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I21" s="7"/>
       <c r="J21" s="7"/>
@@ -2502,7 +2502,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I22" s="7"/>
       <c r="J22" s="7"/>
@@ -2545,7 +2545,7 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I23" s="7"/>
       <c r="J23" s="7"/>
@@ -2588,7 +2588,7 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I24" s="7"/>
       <c r="J24" s="7"/>

--- a/CaesarCipher/Документация/Материалы/Схема.xlsx
+++ b/CaesarCipher/Документация/Материалы/Схема.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
   <si>
     <t>Alphabet</t>
   </si>
@@ -141,9 +141,6 @@
     <t>-operation_ : string</t>
   </si>
   <si>
-    <t>+Animation() : void</t>
-  </si>
-  <si>
     <t>-AnimationTextBox : TextBox</t>
   </si>
   <si>
@@ -154,6 +151,18 @@
   </si>
   <si>
     <t>+OutputResult(originalText, encryptedText, filePath, key) : void</t>
+  </si>
+  <si>
+    <t>+RunAnimationAsync() : Task</t>
+  </si>
+  <si>
+    <t>+CancelButton_Click(sender, e) : void</t>
+  </si>
+  <si>
+    <t>-isCancelled_ : bool</t>
+  </si>
+  <si>
+    <t>-CancelButton : Button</t>
   </si>
 </sst>
 </file>
@@ -306,7 +315,7 @@
       <xdr:col>34</xdr:col>
       <xdr:colOff>538373</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>181097</xdr:rowOff>
+      <xdr:rowOff>181096</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -382,7 +391,7 @@
       <xdr:col>27</xdr:col>
       <xdr:colOff>464877</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>200821</xdr:rowOff>
+      <xdr:rowOff>177009</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -409,56 +418,18 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>197644</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>586352</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66970</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Рисунок 5"/>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="30070425" y="1188244"/>
-          <a:ext cx="4032021" cy="2141039"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>33</xdr:col>
       <xdr:colOff>255234</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>223985</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>107158</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>34</xdr:col>
-      <xdr:colOff>586352</xdr:colOff>
+      <xdr:colOff>554507</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>171563</xdr:rowOff>
+      <xdr:rowOff>169182</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -470,12 +441,12 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="33164109" y="2259954"/>
-          <a:ext cx="938337" cy="4793422"/>
+          <a:off x="34021359" y="1881189"/>
+          <a:ext cx="906492" cy="5193618"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -24239"/>
+            <a:gd name="adj1" fmla="val -25218"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -502,15 +473,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>378886</xdr:colOff>
+      <xdr:colOff>378885</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>54768</xdr:rowOff>
+      <xdr:rowOff>54769</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>28</xdr:col>
-      <xdr:colOff>197644</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>223984</xdr:rowOff>
+      <xdr:colOff>357189</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>107158</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -522,13 +493,13 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1">
-          <a:off x="28731032" y="920559"/>
-          <a:ext cx="431154" cy="2247633"/>
+          <a:off x="29857436" y="651405"/>
+          <a:ext cx="52389" cy="2407179"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector4">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -53315"/>
-            <a:gd name="adj2" fmla="val 92416"/>
+            <a:gd name="adj1" fmla="val -436351"/>
+            <a:gd name="adj2" fmla="val 89624"/>
           </a:avLst>
         </a:prstGeom>
         <a:ln>
@@ -761,13 +732,13 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>31</xdr:col>
-      <xdr:colOff>393187</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>66970</xdr:rowOff>
+      <xdr:colOff>455848</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>214313</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>393011</xdr:colOff>
+      <xdr:colOff>391821</xdr:colOff>
       <xdr:row>17</xdr:row>
       <xdr:rowOff>26194</xdr:rowOff>
     </xdr:to>
@@ -781,8 +752,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm rot="16200000" flipH="1">
-          <a:off x="32232941" y="3183967"/>
-          <a:ext cx="923630" cy="1214261"/>
+          <a:off x="33069582" y="3188361"/>
+          <a:ext cx="1026318" cy="1150410"/>
         </a:xfrm>
         <a:prstGeom prst="bentConnector3">
           <a:avLst/>
@@ -1205,7 +1176,7 @@
       <xdr:col>18</xdr:col>
       <xdr:colOff>588685</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>7353</xdr:rowOff>
+      <xdr:rowOff>7352</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1215,7 +1186,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1234,20 +1205,58 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>357190</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>554507</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>214313</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Рисунок 5"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="31087221" y="511970"/>
+          <a:ext cx="3840630" cy="2738437"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
       <xdr:col>23</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>46</xdr:row>
+      <xdr:row>44</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>41</xdr:col>
-      <xdr:colOff>206342</xdr:colOff>
-      <xdr:row>70</xdr:row>
-      <xdr:rowOff>798</xdr:rowOff>
+      <xdr:colOff>196816</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>77042</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="Рисунок 13"/>
+        <xdr:cNvPr id="11" name="Рисунок 10"/>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1260,8 +1269,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="27693938" y="11168063"/>
-          <a:ext cx="11136279" cy="5715798"/>
+          <a:off x="27693938" y="10715625"/>
+          <a:ext cx="11126753" cy="6030167"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1804,7 +1813,7 @@
       </c>
       <c r="I6" s="7"/>
       <c r="J6" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" s="7"/>
       <c r="L6" s="7"/>
@@ -1853,7 +1862,7 @@
       </c>
       <c r="I7" s="7"/>
       <c r="J7" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K7" s="7"/>
       <c r="L7" s="7"/>
@@ -1892,15 +1901,15 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="4" t="s">
         <v>25</v>
       </c>
       <c r="I8" s="7"/>
-      <c r="J8" s="2" t="s">
-        <v>42</v>
+      <c r="J8" s="4" t="s">
+        <v>40</v>
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -1944,8 +1953,8 @@
         <v>26</v>
       </c>
       <c r="I9" s="7"/>
-      <c r="J9" s="3" t="s">
-        <v>40</v>
+      <c r="J9" s="4" t="s">
+        <v>47</v>
       </c>
       <c r="K9" s="7"/>
       <c r="L9" s="7"/>
@@ -1989,7 +1998,9 @@
         <v>17</v>
       </c>
       <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="7"/>
       <c r="M10" s="7"/>
@@ -2032,7 +2043,9 @@
         <v>18</v>
       </c>
       <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
+      <c r="J11" s="4" t="s">
+        <v>44</v>
+      </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
@@ -2063,7 +2076,7 @@
       <c r="AL11" s="7"/>
       <c r="AM11" s="7"/>
     </row>
-    <row r="12" spans="1:39" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -2075,7 +2088,9 @@
         <v>19</v>
       </c>
       <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
+      <c r="J12" s="3" t="s">
+        <v>45</v>
+      </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
       <c r="M12" s="7"/>
@@ -2106,7 +2121,7 @@
       <c r="AL12" s="7"/>
       <c r="AM12" s="7"/>
     </row>
-    <row r="13" spans="1:39" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" ht="19.5" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
